--- a/Excel_Practice_Files/All Practice Next.xlsx
+++ b/Excel_Practice_Files/All Practice Next.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Cadd Mentor\Student_Class_Code\Jazaul_Hasan_Data_Anylytics\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Cadd Mentor\Student_Class_Code\Jazaul_Hasan_Data_Anylytics\Excel_Practice_Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18AA337A-496F-4F8B-935C-C67DAFB6F0E9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF7BA8F0-1250-4EDA-AF27-28B64EFFE62D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Practice Date Formule" sheetId="1" r:id="rId1"/>
@@ -19,10 +19,12 @@
     <sheet name="Sheet4" sheetId="6" r:id="rId4"/>
     <sheet name="Sheet5" sheetId="7" r:id="rId5"/>
     <sheet name="Sheet6" sheetId="8" r:id="rId6"/>
+    <sheet name="Sheet1" sheetId="9" r:id="rId7"/>
+    <sheet name="Sheet2" sheetId="10" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId7"/>
+    <pivotCache cacheId="0" r:id="rId9"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -33,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="56">
   <si>
     <t>Today</t>
   </si>
@@ -195,6 +197,12 @@
   </si>
   <si>
     <t>Amount</t>
+  </si>
+  <si>
+    <t>RowNumber</t>
+  </si>
+  <si>
+    <t>Column Number</t>
   </si>
 </sst>
 </file>
@@ -1273,6 +1281,76 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F47CC0A2-CB94-463D-B4DC-6F33A7353C3C}" name="PivotTable6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="G17:I22" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="10">
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="3"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <dataFields count="2">
+    <dataField name="Sum of Sale_amt" fld="7" baseField="0" baseItem="0"/>
+    <dataField name="Max of Units" fld="5" subtotal="max" showDataAs="percentOfTotal" baseField="0" baseItem="0" numFmtId="10"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{77AC233B-D4D6-4316-A70E-B7424E7F4DC4}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A12:C17" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
@@ -1342,7 +1420,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F13C8B30-1FA5-4AAE-A9E0-6F3A0FF62570}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:C8" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
@@ -1412,7 +1490,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{848105FE-384B-4BFA-855B-5023E3F4C261}" name="PivotTable8" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="D13:F18" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
@@ -1482,79 +1560,9 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B9703331-90ED-4F0C-9CA9-C15CEFE6327A}" name="PivotTable7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="G9:I14" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="10">
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="5">
-        <item x="3"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="2"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-  </colItems>
-  <dataFields count="2">
-    <dataField name="Sum of Sale_amt" fld="7" baseField="0" baseItem="0"/>
-    <dataField name="Max of Units" fld="5" subtotal="max" showDataAs="percentOfTotal" baseField="0" baseItem="0" numFmtId="10"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F47CC0A2-CB94-463D-B4DC-6F33A7353C3C}" name="PivotTable6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="G17:I22" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField numFmtId="14" showAll="0"/>
     <pivotField showAll="0"/>
@@ -1952,11 +1960,11 @@
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="4">
         <f ca="1">TODAY()</f>
-        <v>46049</v>
+        <v>46118</v>
       </c>
       <c r="B2" s="5">
         <f ca="1">NOW()</f>
-        <v>46049.46202673611</v>
+        <v>46118.467890740743</v>
       </c>
       <c r="C2">
         <f ca="1">YEAR(B2)</f>
@@ -1964,11 +1972,11 @@
       </c>
       <c r="D2">
         <f ca="1">MONTH(B2)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E2">
         <f ca="1">DAY(B2)</f>
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="F2">
         <f ca="1">HOUR(B2)</f>
@@ -1976,21 +1984,21 @@
       </c>
       <c r="G2">
         <f ca="1">MINUTE(B2)</f>
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="H2">
         <f ca="1">SECOND(B2)</f>
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="I2" s="5">
         <f ca="1">EDATE(A2,4)</f>
-        <v>46169</v>
+        <v>46240</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="I4" s="4">
         <f ca="1">EDATE(A2,3*12)</f>
-        <v>47145</v>
+        <v>47214</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
@@ -5252,4 +5260,361 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF981F1C-A61A-406B-B7D9-1BA8829F7B65}">
+  <dimension ref="A1:I12"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.77734375" customWidth="1"/>
+    <col min="6" max="6" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="26" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" s="9">
+        <v>95</v>
+      </c>
+      <c r="D2" s="9">
+        <v>1198</v>
+      </c>
+      <c r="E2" s="9">
+        <v>113810</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" s="9">
+        <v>36</v>
+      </c>
+      <c r="D3" s="9">
+        <v>1198</v>
+      </c>
+      <c r="E3" s="9">
+        <v>43128</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="9">
+        <v>27</v>
+      </c>
+      <c r="D4" s="9">
+        <v>225</v>
+      </c>
+      <c r="E4" s="9">
+        <v>6075</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="11">
+        <v>56</v>
+      </c>
+      <c r="D5" s="11">
+        <v>1198</v>
+      </c>
+      <c r="E5" s="11">
+        <v>67088</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="G5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5">
+        <f>MATCH(G5,A2:A6,0)</f>
+        <v>4</v>
+      </c>
+      <c r="I5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="9">
+        <v>75</v>
+      </c>
+      <c r="D6" s="9">
+        <v>1198</v>
+      </c>
+      <c r="E6" s="9">
+        <v>89850</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="9"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="10"/>
+      <c r="G7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7">
+        <f>MATCH(G7,A1:F1,0)</f>
+        <v>5</v>
+      </c>
+      <c r="I7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H9">
+        <f>INDEX(A1:F6,3,3)</f>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="E10" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10">
+        <f>VLOOKUP(E10,A1:F6,5,FALSE)</f>
+        <v>67088</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G12" t="s">
+        <v>22</v>
+      </c>
+      <c r="H12">
+        <f>INDEX(A1:F6,MATCH(G12,A1:A6,0),MATCH(H11,A1:F1,0))</f>
+        <v>225</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E10 G12" xr:uid="{C2FF0DE4-FFEB-40A3-90B2-34CF47904836}">
+      <formula1>$A$2:$A$6</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H11" xr:uid="{F106E82A-F4A0-4CFE-811A-83A437C4C094}">
+      <formula1>$B$1:$F$1</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D64FF50B-95A7-4FF3-BEC7-4B424575FC3A}">
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="9">
+        <v>95</v>
+      </c>
+      <c r="C3" s="9">
+        <v>36</v>
+      </c>
+      <c r="D3" s="9">
+        <v>27</v>
+      </c>
+      <c r="E3" s="11">
+        <v>56</v>
+      </c>
+      <c r="F3" s="9">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="9">
+        <v>1198</v>
+      </c>
+      <c r="C4" s="9">
+        <v>1198</v>
+      </c>
+      <c r="D4" s="9">
+        <v>225</v>
+      </c>
+      <c r="E4" s="11">
+        <v>1198</v>
+      </c>
+      <c r="F4" s="9">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="9">
+        <v>113810</v>
+      </c>
+      <c r="C5" s="9">
+        <v>43128</v>
+      </c>
+      <c r="D5" s="9">
+        <v>6075</v>
+      </c>
+      <c r="E5" s="11">
+        <v>67088</v>
+      </c>
+      <c r="F5" s="9">
+        <v>89850</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" t="str">
+        <f>HLOOKUP(C9,A1:F6,6,FALSE)</f>
+        <v>DEBIT CARD</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D11">
+        <f>HLOOKUP(D1,A1:F6,4,FALSE)</f>
+        <v>225</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>